--- a/data/trans_orig/IP07C20-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07C20-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2007 (tasa de respuesta: 89,89%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as en 2007 (tasa de respuesta: 89,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14520</t>
+          <t>14044</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6194</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15494</t>
+          <t>14821</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13972</t>
+          <t>13714</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26813</t>
+          <t>26084</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12207</t>
+          <t>12300</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22991</t>
+          <t>23135</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11459</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21262</t>
+          <t>21567</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>49,19%</t>
+          <t>49,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>26243</t>
+          <t>25869</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40728</t>
+          <t>40726</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>8661</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>18467</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11126</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20892</t>
+          <t>20597</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22173</t>
+          <t>22420</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35950</t>
+          <t>36519</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,92%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9120</t>
+          <t>9402</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4221</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3214</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11439</t>
+          <t>11567</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4455</t>
+          <t>4588</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4594</t>
+          <t>4194</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27902</t>
+          <t>29129</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45314</t>
+          <t>45963</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40902</t>
+          <t>41137</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>60170</t>
+          <t>61208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74285</t>
+          <t>75093</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101435</t>
+          <t>101601</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81797</t>
+          <t>80165</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104593</t>
+          <t>103079</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77878</t>
+          <t>76032</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>100173</t>
+          <t>100354</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163406</t>
+          <t>166906</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>196401</t>
+          <t>195773</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,02%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44010</t>
+          <t>43862</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63270</t>
+          <t>64119</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55296</t>
+          <t>54707</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>76884</t>
+          <t>77507</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>103705</t>
+          <t>103496</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>132354</t>
+          <t>131982</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,37%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2140</t>
+          <t>2530</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9664</t>
+          <t>10268</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14765</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>9119</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20591</t>
+          <t>20404</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>713</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6560</t>
+          <t>6670</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7844</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11710</t>
+          <t>11449</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12387</t>
+          <t>12500</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23517</t>
+          <t>23434</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,35%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14133</t>
+          <t>13668</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24743</t>
+          <t>24881</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>28800</t>
+          <t>29143</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44498</t>
+          <t>44725</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17438</t>
+          <t>17937</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29436</t>
+          <t>29657</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>33,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15566</t>
+          <t>15005</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26083</t>
+          <t>25964</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>35737</t>
+          <t>35860</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52843</t>
+          <t>51958</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,3%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15449</t>
+          <t>16065</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4774</t>
+          <t>4330</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13254</t>
+          <t>13383</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12582</t>
+          <t>13278</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25933</t>
+          <t>26029</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>5071</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>3533</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>694</t>
+          <t>695</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>52546</t>
+          <t>51938</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>75199</t>
+          <t>75725</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>67399</t>
+          <t>67406</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>92690</t>
+          <t>92827</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>127934</t>
+          <t>127119</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>160549</t>
+          <t>160531</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118824</t>
+          <t>118809</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>146235</t>
+          <t>147012</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>112363</t>
+          <t>111760</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>139751</t>
+          <t>140026</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,14%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>237900</t>
+          <t>240181</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>278224</t>
+          <t>278679</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,43%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>66036</t>
+          <t>66049</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>91705</t>
+          <t>90556</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>77127</t>
+          <t>76117</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>103249</t>
+          <t>101520</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>147749</t>
+          <t>149753</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>184743</t>
+          <t>185089</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6618</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18012</t>
+          <t>18501</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>5851</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16606</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15722</t>
+          <t>15812</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30857</t>
+          <t>30480</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10295</t>
+          <t>10217</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8498</t>
+          <t>9139</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5609</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15416</t>
+          <t>15647</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2012 (tasa de respuesta: 95,31%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as en 2012 (tasa de respuesta: 95,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14365</t>
+          <t>13796</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26061</t>
+          <t>24950</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>48,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>11176</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22583</t>
+          <t>21843</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27518</t>
+          <t>28083</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>43659</t>
+          <t>44061</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8073</t>
+          <t>8139</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17822</t>
+          <t>18130</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>7165</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16990</t>
+          <t>16929</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>17478</t>
+          <t>17056</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31945</t>
+          <t>31220</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,26%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9454</t>
+          <t>9158</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19855</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>17445</t>
+          <t>16948</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19404</t>
+          <t>19474</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>34193</t>
+          <t>34376</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10036</t>
+          <t>10389</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1249</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7130</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4728</t>
+          <t>4814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14678</t>
+          <t>14314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54249</t>
+          <t>52033</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75047</t>
+          <t>73908</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63754</t>
+          <t>65012</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86286</t>
+          <t>86751</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121942</t>
+          <t>122584</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>153779</t>
+          <t>155538</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>36,9%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67522</t>
+          <t>67345</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89490</t>
+          <t>90959</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68680</t>
+          <t>69711</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92904</t>
+          <t>93171</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>143969</t>
+          <t>142725</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>177318</t>
+          <t>175842</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,07%</t>
+          <t>41,72%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37117</t>
+          <t>37822</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>57280</t>
+          <t>57045</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40762</t>
+          <t>39509</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>61312</t>
+          <t>58411</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>83968</t>
+          <t>82403</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>111178</t>
+          <t>110441</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10046</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>17471</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11026</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>23645</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7224</t>
+          <t>7339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13479</t>
+          <t>12237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6078</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16890</t>
+          <t>17050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25393</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>37193</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15313</t>
+          <t>15241</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26560</t>
+          <t>26586</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42805</t>
+          <t>43708</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60360</t>
+          <t>60929</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,1%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>14913</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25623</t>
+          <t>26763</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17126</t>
+          <t>17482</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29038</t>
+          <t>29167</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34512</t>
+          <t>35316</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>51509</t>
+          <t>51495</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>5091</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14580</t>
+          <t>13954</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4533</t>
+          <t>4410</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13566</t>
+          <t>13760</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11922</t>
+          <t>12253</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25710</t>
+          <t>25535</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,83%</t>
         </is>
       </c>
     </row>
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>782</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7828</t>
+          <t>8177</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>764</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7527</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4793</t>
+          <t>4737</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>101240</t>
+          <t>100830</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>128582</t>
+          <t>129665</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>98207</t>
+          <t>96875</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>125520</t>
+          <t>127108</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>207350</t>
+          <t>208182</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>247499</t>
+          <t>247271</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>97198</t>
+          <t>98393</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>125743</t>
+          <t>124808</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>102862</t>
+          <t>101628</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>130872</t>
+          <t>130403</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>206826</t>
+          <t>207188</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>247382</t>
+          <t>245751</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58621</t>
+          <t>58727</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>84000</t>
+          <t>83714</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>58223</t>
+          <t>58355</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>82630</t>
+          <t>82342</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>122312</t>
+          <t>123759</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>156617</t>
+          <t>156875</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17869</t>
+          <t>17782</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>11069</t>
+          <t>11512</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>25285</t>
+          <t>25287</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21165</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>38268</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7029</t>
+          <t>7415</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>5745</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17116</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8216</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20222</t>
+          <t>20952</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de tener suficiente dinero para hacer lo mismo que sus amigos/as en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1851</t>
+          <t>1556</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8227</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>10525</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>6059</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15729</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,95%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>10079</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20485</t>
+          <t>20399</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15217</t>
+          <t>14596</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27858</t>
+          <t>27145</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>40,37%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9420</t>
+          <t>9945</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18731</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4796</t>
+          <t>4608</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13301</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16265</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29813</t>
+          <t>28992</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>43,11%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>10916</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17434</t>
+          <t>16965</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,23%</t>
         </is>
       </c>
     </row>
@@ -7107,7 +7107,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4813</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7142,7 +7142,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43983</t>
+          <t>44409</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65959</t>
+          <t>66990</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47423</t>
+          <t>48427</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69311</t>
+          <t>71112</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>97294</t>
+          <t>98885</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>128809</t>
+          <t>128585</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74837</t>
+          <t>74511</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100729</t>
+          <t>98882</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72429</t>
+          <t>73472</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>98657</t>
+          <t>99146</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>154819</t>
+          <t>154168</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190393</t>
+          <t>191898</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>40,01%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>58352</t>
+          <t>58517</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>82099</t>
+          <t>81392</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59234</t>
+          <t>57850</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83519</t>
+          <t>81458</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,99%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>124080</t>
+          <t>123679</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>158011</t>
+          <t>157777</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13885</t>
+          <t>13732</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28036</t>
+          <t>27834</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9899</t>
+          <t>9612</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22866</t>
+          <t>22673</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26458</t>
+          <t>27631</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45297</t>
+          <t>46970</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6879</t>
+          <t>6893</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17566</t>
+          <t>17589</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13116</t>
+          <t>13380</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>12764</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27386</t>
+          <t>26863</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24002</t>
+          <t>23904</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37738</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>16432</t>
+          <t>17093</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29122</t>
+          <t>30940</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>43724</t>
+          <t>44126</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63147</t>
+          <t>63958</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,87%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>12226</t>
+          <t>10946</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25065</t>
+          <t>24057</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23781</t>
+          <t>24396</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38533</t>
+          <t>37757</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38986</t>
+          <t>39014</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58363</t>
+          <t>58220</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,93%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10982</t>
+          <t>10993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22990</t>
+          <t>23091</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12916</t>
+          <t>11564</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25925</t>
+          <t>25213</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26367</t>
+          <t>26558</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>44272</t>
+          <t>43312</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,71%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1503</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8502</t>
+          <t>9009</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>635</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8408,7 +8408,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3483</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12119</t>
+          <t>12497</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -8471,7 +8471,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3878</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>3202</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>519</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4636</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>76587</t>
+          <t>77235</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>105898</t>
+          <t>103648</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>74724</t>
+          <t>73514</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>102420</t>
+          <t>101442</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>161167</t>
+          <t>159706</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>198240</t>
+          <t>198572</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>95880</t>
+          <t>96745</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>126221</t>
+          <t>124864</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>115819</t>
+          <t>116574</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>145904</t>
+          <t>146837</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>220606</t>
+          <t>220546</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>261094</t>
+          <t>261124</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,7%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>85981</t>
+          <t>87073</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>114152</t>
+          <t>115098</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>84717</t>
+          <t>83909</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>112882</t>
+          <t>110979</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>178407</t>
+          <t>178874</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>215090</t>
+          <t>217021</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>21503</t>
+          <t>21715</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>38619</t>
+          <t>38419</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16960</t>
+          <t>16626</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32874</t>
+          <t>32753</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>43187</t>
+          <t>43077</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>66899</t>
+          <t>66043</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20336</t>
+          <t>20070</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14805</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15586</t>
+          <t>15747</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30492</t>
+          <t>31267</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
